--- a/progress/Unit_Test_Plan_v0.1.xlsx
+++ b/progress/Unit_Test_Plan_v0.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ganesh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ganesh\ai-security-analysis-agent\progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7AF5A3-CBC9-4EB2-A828-CC711049A37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A34B6EEB-21F1-4837-A41D-1C12612F78D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12336" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
   <sheets>
     <sheet name="UT" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Actual Result</t>
   </si>
@@ -82,6 +82,96 @@
   </si>
   <si>
     <t>As expected, Java was auto-detected and passed structural syntax validation.</t>
+  </si>
+  <si>
+    <t>Verify AST &amp; Tree-sitter Syntax Gatekeeper Blocks Invalid Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paste a Python snippet missing a colon : or a Java snippet missing a semicolon ; and click "Run SAST + Parallel Multi-Agent Analysis".   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syntax gatekeeper (parsers/code_validator.py) should catch the syntax error via AST/Tree-sitter and block downstream agents from executing.   </t>
+  </si>
+  <si>
+    <t>UI displays Syntax Error on Line X, shows the offending line, and prevents LLM agents from being triggered.</t>
+  </si>
+  <si>
+    <t>As expected, the gatekeeper blocked agent execution and displayed the exact line number and offending syntax.</t>
+  </si>
+  <si>
+    <t>Verify Code Analysis Agent Detects Smells &amp; Design Anti-Patterns</t>
+  </si>
+  <si>
+    <t>Verify Parallel Multi-Agent Execution &amp; Unified Severity Scoring</t>
+  </si>
+  <si>
+    <t>Verify FastAPI Backend Endpoint &amp; SQLite History Persistence</t>
+  </si>
+  <si>
+    <t>Submit sample_codes/vulnerable_python_sample.py and inspect the Quality Assessment and Complexity cards on the right panel.</t>
+  </si>
+  <si>
+    <t>Submit sample code containing SQL Injection, Hardcoded Secrets, Weak MD5 Hashing, and Command Injection, then expand findings in the Security Vulnerability Report tab.</t>
+  </si>
+  <si>
+    <t>Verify Security Vulnerability Agent &amp; 6 Mandatory Report Fields.</t>
+  </si>
+  <si>
+    <t>Verify Layer 2 SAST &amp; 4-Complexity Metrics Calculation.</t>
+  </si>
+  <si>
+    <t>Run analysis on VulnerableJavaSample.java and inspect the Unified Findings Report tab and Stage 6: Severity Scoring Breakdown</t>
+  </si>
+  <si>
+    <t>Run an analysis in Streamlit and open the SQLite History tab (or call GET [http://127.0.0.1:8000/api/v1/history](http://127.0.0.1:8000/api/v1/history)).</t>
+  </si>
+  <si>
+    <t>Submit Python/Java sample code containing deep nesting, magic numbers, and empty except/catch blocks, then open the Code Analysis Report tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tools/static_analyzer.py should compute Cyclomatic, Cognitive, Time ($O$), and Space ($O$) complexity plus Maintainability, Duplication %, Documentation %, and Tech Debt.   </t>
+  </si>
+  <si>
+    <t>Code Analysis Agent should detect code smells and the 6 Design Anti-Patterns (e.g., Spaghetti Code, Lava Flow, God Object, Empty Catch Block) with severity and line numbers.</t>
+  </si>
+  <si>
+    <t>Security Vulnerability Agent should combine SAST alerts (Bandit, Semgrep, SpotBugs) with OWASP RAG context and output all 6 required security report fields.</t>
+  </si>
+  <si>
+    <t>LangGraph (src/workflow.py) should execute Code Analysis and Security agents in parallel and merge findings sorted from Critical to Informational.</t>
+  </si>
+  <si>
+    <t>FastAPI (services/api.py) and services/database.py should persist every completed review into data/reviews.db.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right panel displays all 5 Quality Assessment metrics and all 4 Complexity metrics (Cyclomatic, Cognitive, Time, Space).   </t>
+  </si>
+  <si>
+    <t>Code Analysis tab lists each smell/anti-pattern with exact line reference, severity badge, description, and refactoring recommendation.</t>
+  </si>
+  <si>
+    <t>Each finding displays: (1) Vulnerability Name, (2) Severity Level, (3) Affected Line Number, (4) Risk Description, (5) Recommendation, and (6) Secure Coding Suggestion.</t>
+  </si>
+  <si>
+    <t>Unified Findings count equals the sum of both agents, sorted by severity (Critical, High, Medium, Low, Informational).</t>
+  </si>
+  <si>
+    <t>The SQLite History tab displays the newly recorded review row with timestamp, filename, language, maintainability score, and finding counts.</t>
+  </si>
+  <si>
+    <t>As expected, all 4 complexity metrics and 5 quality scores were accurately calculated and displayed.</t>
+  </si>
+  <si>
+    <t>As expected, the Code Analysis Agent accurately flagged Spaghetti Code, Magic Numbers, Unclosed Resources, and Empty Catch Blocks.</t>
+  </si>
+  <si>
+    <t>As expected, all OWASP vulnerabilities were flagged at their exact line numbers with complete 6-field reports and secure code examples.</t>
+  </si>
+  <si>
+    <t>As expected, both agents ran concurrently in LangGraph and produced a merged, severity-sorted Unified Findings Report.</t>
+  </si>
+  <si>
+    <t>As expected, the review record was saved to data/reviews.db and rendered in the SQLite History table.</t>
   </si>
 </sst>
 </file>
@@ -130,7 +220,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -153,11 +243,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -170,6 +271,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -485,7 +598,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -555,29 +668,125 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+    <row r="4" spans="1:6" ht="171.6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="202.8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="202.8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="218.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="187.2" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="202.8" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
